--- a/ESERCIZIO_M2-1-3_dati grafici.xlsx
+++ b/ESERCIZIO_M2-1-3_dati grafici.xlsx
@@ -5,10 +5,10 @@
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bbcc35c869531aa5/Escritorio/Data Analyst/Settimana 1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bbcc35c869531aa5/Dokumenti/GitHub/Fist-project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{381F57C5-93E0-49A3-87E4-91599A517222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4956456F-0B15-430D-A7BA-4001992FDDC7}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{381F57C5-93E0-49A3-87E4-91599A517222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE4A46BC-A625-4315-AA0E-CEEB8BD632EA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>CIBO</t>
   </si>
@@ -174,6 +174,9 @@
   <si>
     <t xml:space="preserve">Cambiamenti di pesso in relazione al giorno </t>
   </si>
+  <si>
+    <t>m</t>
+  </si>
 </sst>
 </file>
 
@@ -182,7 +185,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -217,6 +220,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -238,7 +248,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -247,6 +257,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -6888,7 +6899,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z16"/>
+  <dimension ref="A1:Z19"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.33203125" customWidth="1"/>
@@ -7134,6 +7145,11 @@
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
     </row>
+    <row r="19" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E19" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B13:F16"/>
